--- a/xxx测试计划.xlsx
+++ b/xxx测试计划.xlsx
@@ -493,7 +493,8 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mysql</t>
+          <t>mysql
+sqlserver</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +517,11 @@
           <t>无</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -616,7 +621,11 @@
           <t>无</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -659,7 +668,11 @@
           <t>无</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -721,7 +734,11 @@
           <t>无</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -787,7 +804,11 @@
           <t>无</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -891,7 +912,11 @@
           <t>无</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/xxx测试计划.xlsx
+++ b/xxx测试计划.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>模块A</t>
+          <t>模块B</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -517,11 +517,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -603,7 +599,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>模块A</t>
+          <t>模块B</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -621,11 +617,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -650,7 +642,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>模块A</t>
+          <t>模块B</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -668,11 +660,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -716,7 +704,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>模块A</t>
+          <t>模块B</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -734,11 +722,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -786,7 +770,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>模块A</t>
+          <t>模块B</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -804,11 +788,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -894,7 +874,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>模块A</t>
+          <t>模块B</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -912,11 +892,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
